--- a/AAII_Financials/Yearly/TANH_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TANH_YR_FIN.xlsx
@@ -1008,7 +1008,7 @@
         <v>9</v>
       </c>
       <c r="D14" s="3">
-        <v>-5800</v>
+        <v>19700</v>
       </c>
       <c r="E14" s="3">
         <v>1200</v>
@@ -1059,13 +1059,13 @@
         <v>10</v>
       </c>
       <c r="D15" s="3">
-        <v>17400</v>
+        <v>0</v>
       </c>
       <c r="E15" s="3">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="F15" s="3">
-        <v>900</v>
+        <v>200</v>
       </c>
       <c r="G15" s="3">
         <v>1000</v>
@@ -1251,7 +1251,7 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>27100</v>
+        <v>2000</v>
       </c>
       <c r="E20" s="3">
         <v>3700</v>
@@ -1302,13 +1302,13 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>-22000</v>
+        <v>-14200</v>
       </c>
       <c r="E21" s="3">
-        <v>1800</v>
+        <v>300</v>
       </c>
       <c r="F21" s="3">
-        <v>4900</v>
+        <v>4200</v>
       </c>
       <c r="G21" s="3">
         <v>7000</v>
@@ -1863,7 +1863,7 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-27100</v>
+        <v>-2000</v>
       </c>
       <c r="E32" s="3">
         <v>-3700</v>
@@ -2267,10 +2267,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>37800</v>
+        <v>40200</v>
       </c>
       <c r="E43" s="3">
-        <v>75700</v>
+        <v>77300</v>
       </c>
       <c r="F43" s="3">
         <v>84300</v>
@@ -2372,7 +2372,7 @@
         <v>100</v>
       </c>
       <c r="E45" s="3">
-        <v>5200</v>
+        <v>4700</v>
       </c>
       <c r="F45" s="3">
         <v>1800</v>
@@ -3023,10 +3023,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4600</v>
+        <v>6100</v>
       </c>
       <c r="E59" s="3">
-        <v>6500</v>
+        <v>7600</v>
       </c>
       <c r="F59" s="3">
         <v>3900</v>
@@ -4399,7 +4399,7 @@
         <v>-5800</v>
       </c>
       <c r="E89" s="3">
-        <v>4000</v>
+        <v>5400</v>
       </c>
       <c r="F89" s="3">
         <v>5300</v>
@@ -4624,7 +4624,7 @@
         <v>-1100</v>
       </c>
       <c r="E94" s="3">
-        <v>-1900</v>
+        <v>-3300</v>
       </c>
       <c r="F94" s="3">
         <v>-2600</v>
